--- a/retail-ai-platform/docs/samples/column_mapping_template_v1.xlsx
+++ b/retail-ai-platform/docs/samples/column_mapping_template_v1.xlsx
@@ -678,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -995,12 +995,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>YES*</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Line amount before discount, in currency</t>
+          <t>Line amount BEFORE discount. *Required unless net_amount is mapped</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>discount_amount</t>
+          <t>net_amount</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES*</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Discount amount on the line</t>
+          <t>Line amount AFTER discount (check on the client file which one it is). Map this OR gross_amount; gross = net + discount</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>65000</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>vat_amount</t>
+          <t>discount_amount</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>VAT amount if shown separately</t>
+          <t>Discount amount on the line</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>5000</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>cogs_amount</t>
+          <t>vat_amount</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>no*</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Cost of goods for the line. *Required for gross profit; if absent, profit KPIs are flagged 'no COGS'</t>
+          <t>VAT amount if shown separately</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44000</t>
+          <t>10833</t>
         </is>
       </c>
     </row>
@@ -1113,27 +1113,27 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>cogs_amount</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no*</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Storage / shop</t>
+          <t>Cost of goods for the line. *Required for gross profit; if absent, profit KPIs are flagged 'no COGS'</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Խանութ Կենտրոն</t>
+          <t>44000</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1160,44 +1160,44 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ISO 4217; default from File settings</t>
+          <t>Storage / shop</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Խանութ Կենտրոն</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>InventorySnapshot (ՀԾ մնացորդ)</t>
+          <t>SaleLine (ՀԾ վաճառք/վերադարձ)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>as_of_date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Date of the balance (usually export date)</t>
+          <t>ISO 4217; default from File settings</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>AMD</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>sku_code</t>
+          <t>as_of_date</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Product code</t>
+          <t>Date of the balance (usually export date)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>A-1045</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>sku_name</t>
+          <t>sku_code</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Product name</t>
+          <t>Product code</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Վերնաշապիկ սպիտակ M</t>
+          <t>A-1045</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>sku_name</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Product name</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Պահեստ 1</t>
+          <t>Վերնաշապիկ սպիտակ M</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>On-hand quantity</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>Պահեստ 1</t>
         </is>
       </c>
     </row>
@@ -1337,27 +1337,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>On-hand quantity</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>հատ</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -1369,27 +1369,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>cost_per_unit</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>no*</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Unit cost (*needed for stock value and GP)</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>հատ</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>sale_price</t>
+          <t>cost_per_unit</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1411,49 +1411,49 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no*</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Current sale price</t>
+          <t>Unit cost (*needed for stock value and GP)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>22000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CampaignDaily (Meta / TikTok)</t>
+          <t>InventorySnapshot (ՀԾ մնացորդ)</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>sale_price</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>meta | tiktok (set in File settings, not a column)</t>
+          <t>Current sale price</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>35000</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Reporting day</t>
+          <t>meta | tiktok (set in File settings, not a column)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>meta</t>
         </is>
       </c>
     </row>
@@ -1497,27 +1497,27 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>campaign_id</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>no*</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Campaign ID (*if absent, campaign_name is used as key)</t>
+          <t>Reporting day</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23851234567890123</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>campaign_name</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1539,17 +1539,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no*</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Campaign name</t>
+          <t>Campaign ID (*if absent, campaign_name is used as key)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Autumn_Shirts_Conv</t>
+          <t>23851234567890123</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>adset_name</t>
+          <t>campaign_name</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Ad set name</t>
+          <t>Campaign name</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Yerevan_25-45</t>
+          <t>Autumn_Shirts_Conv</t>
         </is>
       </c>
     </row>
@@ -1593,27 +1593,27 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>spend</t>
+          <t>adset_name</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Amount spent</t>
+          <t>Ad set name</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>Yerevan_25-45</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>impressions</t>
+          <t>spend</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1635,17 +1635,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Impressions</t>
+          <t>Amount spent</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48210</t>
+          <t>12500</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>clicks</t>
+          <t>impressions</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Link clicks</t>
+          <t>Impressions</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>48210</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>results</t>
+          <t>clicks</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Results / purchases as reported by platform (NOT incremental sales)</t>
+          <t>Link clicks</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>640</t>
         </is>
       </c>
     </row>
@@ -1721,39 +1721,39 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>results</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Ad account currency</t>
+          <t>Results / purchases as reported by platform (NOT incremental sales)</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>BankTransaction (քաղվածք)</t>
+          <t>CampaignDaily (Meta / TikTok)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>txn_id</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1763,17 +1763,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>no*</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Bank transaction reference (*if absent, a hash of date+amount+balance+description is used)</t>
+          <t>Ad account currency</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TRX-88213</t>
+          <t>AMD</t>
         </is>
       </c>
     </row>
@@ -1785,27 +1785,27 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>occurred_at</t>
+          <t>txn_id</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no*</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Booking date/time</t>
+          <t>Bank transaction reference (*if absent, a hash of date+amount+balance+description is used)</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:02</t>
+          <t>TRX-88213</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>occurred_at</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Signed amount: credit positive, debit negative (or two columns: see File settings)</t>
+          <t>Booking date/time</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>2026-09-14 11:02</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ISO 4217</t>
+          <t>Signed amount: credit positive, debit negative (or two columns: see File settings)</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
@@ -1881,27 +1881,27 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>balance_after</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Balance after transaction</t>
+          <t>ISO 4217</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2340000</t>
+          <t>AMD</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>balance_after</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1928,12 +1928,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Payment purpose — counterparty names are masked on import</t>
+          <t>Balance after transaction</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Վաճառքից մուտք POS</t>
+          <t>2340000</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>counterparty_account</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1960,24 +1960,24 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Used ONLY to detect transfers between the client's own accounts; then masked</t>
+          <t>Payment purpose — counterparty names are masked on import</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1570...0001</t>
+          <t>Վաճառքից մուտք POS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ReturnLine (եթե առանձին ցանկ)</t>
+          <t>BankTransaction (քաղվածք)</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>source_record_id</t>
+          <t>counterparty_account</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1987,17 +1987,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Unique id of the return line</t>
+          <t>Used ONLY to detect transfers between the client's own accounts; then masked</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Վ-0031/1</t>
+          <t>1570...0001</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>occurred_at</t>
+          <t>source_record_id</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Return date</t>
+          <t>Unique id of the return line</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>Վ-0031/1</t>
         </is>
       </c>
     </row>
@@ -2041,27 +2041,27 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>original_document_number</t>
+          <t>occurred_at</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Sale document being returned</t>
+          <t>Return date</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Հ-00123</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>sku_code</t>
+          <t>original_document_number</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Product code</t>
+          <t>Sale document being returned</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>A-1045</t>
+          <t>Հ-00123</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>sku_code</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Returned quantity (positive)</t>
+          <t>Product code</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>A-1045</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>refund_amount</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Refunded amount</t>
+          <t>Returned quantity (positive)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2169,25 +2169,57 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
+          <t>refund_amount</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Refunded amount</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>32500</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>ReturnLine (եթե առանձին ցանկ)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
@@ -2204,7 +2236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2379,6 +2411,8 @@
       </c>
       <c r="B15" s="4" t="inlineStr"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -2634,7 +2668,7 @@
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>YES*</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2644,7 +2678,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Line amount before discount, in currency</t>
+          <t>Line amount BEFORE discount. *Required unless net_amount is mapped</t>
         </is>
       </c>
       <c r="G27" s="4" t="n"/>
@@ -2652,14 +2686,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>discount_amount</t>
+          <t>net_amount</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES*</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2669,7 +2703,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Discount amount on the line</t>
+          <t>Line amount AFTER discount (check on the client file which one it is). Map this OR gross_amount; gross = net + discount</t>
         </is>
       </c>
       <c r="G28" s="4" t="n"/>
@@ -2677,7 +2711,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>vat_amount</t>
+          <t>discount_amount</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -2694,7 +2728,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>VAT amount if shown separately</t>
+          <t>Discount amount on the line</t>
         </is>
       </c>
       <c r="G29" s="4" t="n"/>
@@ -2702,14 +2736,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>cogs_amount</t>
+          <t>vat_amount</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>no*</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2719,7 +2753,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Cost of goods for the line. *Required for gross profit; if absent, profit KPIs are flagged 'no COGS'</t>
+          <t>VAT amount if shown separately</t>
         </is>
       </c>
       <c r="G30" s="4" t="n"/>
@@ -2727,24 +2761,24 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>warehouse</t>
+          <t>cogs_amount</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no*</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Storage / shop</t>
+          <t>Cost of goods for the line. *Required for gross profit; if absent, profit KPIs are flagged 'no COGS'</t>
         </is>
       </c>
       <c r="G31" s="4" t="n"/>
@@ -2752,7 +2786,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -2769,10 +2803,35 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>Storage / shop</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>ISO 4217; default from File settings</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2966,6 +3025,8 @@
       </c>
       <c r="B15" s="4" t="inlineStr"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -3403,6 +3464,8 @@
       </c>
       <c r="B15" s="4" t="inlineStr"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -3890,6 +3953,8 @@
       </c>
       <c r="B15" s="4" t="inlineStr"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4302,6 +4367,8 @@
       </c>
       <c r="B15" s="4" t="inlineStr"/>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4693,6 +4760,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
